--- a/samples/backbone_500_ingest.xlsx
+++ b/samples/backbone_500_ingest.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JAWA7;LBE;NSRLA;SRLYA;JAWA910;PRIDK;MTWAR;CLMYA;CRATA;SGLNG;ADPLA;CLCAP;BTANG;NTJTI;TJATI;GRSIK;GRATI;PITON</t>
+          <t>JAWA7;LBE7;NSRLA7;SRLYA7;JAWA9107;PRIDK7;MTWAR7;CLMYA7;CRATA7;SGLNG7;ADPLA7;CLCAP7;BTANG7;NTJTI7;TJATI7;GRSIK7;GRATI7;PITON7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT_LBE</t>
+          <t>KIT_LBE7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT_NSRLA</t>
+          <t>KIT_NSRLA7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT_SRLYA</t>
+          <t>KIT_SRLYA7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KIT_JAWA910</t>
+          <t>KIT_JAWA9107</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT_PRIDK</t>
+          <t>KIT_PRIDK7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT_MTWAR</t>
+          <t>KIT_MTWAR7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KIT_CLMYA</t>
+          <t>KIT_CLMYA7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KIT_CRATA</t>
+          <t>KIT_CRATA7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KIT_SGLNG</t>
+          <t>KIT_SGLNG7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KIT_ADPLA</t>
+          <t>KIT_ADPLA7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KIT_CLCAP</t>
+          <t>KIT_CLCAP7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KIT_BTANG</t>
+          <t>KIT_BTANG7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KIT_NTJTI</t>
+          <t>KIT_NTJTI7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KIT_TJATI</t>
+          <t>KIT_TJATI7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KIT_GRSIK</t>
+          <t>KIT_GRSIK7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KIT_GRATI</t>
+          <t>KIT_GRATI7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KIT_PITON</t>
+          <t>KIT_PITON7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DLTMS</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SUTET JAWA7 - BLRJA</t>
+          <t>SUTET JAWA7 - BLRJA7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SUTET JAWA7 - LBE</t>
+          <t>SUTET JAWA7 - LBE7</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SUTET SRLYA - NSRLA</t>
+          <t>SUTET SRLYA7 - NSRLA7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3788,17 +3788,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUTET NSRLA - LBE</t>
+          <t>SUTET NSRLA7 - LBE7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUTET SRLYA - BLRJA</t>
+          <t>SUTET SRLYA7 - BLRJA7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3908,17 +3908,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUTET SRLYA - CLGON</t>
+          <t>SUTET SRLYA7 - CLGON7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3966,17 +3966,17 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUTET JAWA910 - CLGON</t>
+          <t>SUTET JAWA9107 - CLGON7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUTET BLRJA - LNGKG</t>
+          <t>SUTET BLRJA7 - LNGKG7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4084,17 +4084,17 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUTET LBE - BLRJA</t>
+          <t>SUTET LBE7 - BLRJA7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>BLRJA7</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUTET CLGON - CIBNG</t>
+          <t>SUTET CLGON7 - CIBNG7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLGON</t>
+          <t>CLGON7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4204,17 +4204,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUTET GNDUL - DEPOK</t>
+          <t>SUTET GNDUL7 - DEPOK7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUTET DEPOK - CIBNG</t>
+          <t>SUTET DEPOK7 - CIBNG7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4322,17 +4322,17 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUTET LNGKG - GNDUL</t>
+          <t>SUTET LNGKG7 - GNDUL7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LNGKG</t>
+          <t>LNGKG7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4380,17 +4380,17 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUTET KMBNG - GNDUL</t>
+          <t>SUTET KMBNG7 - GNDUL7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUTET GNDUL - DKSBI</t>
+          <t>SUTET GNDUL7 - DKSBI7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4498,17 +4498,17 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUTET KMBNG - DKSBI</t>
+          <t>SUTET KMBNG7 - DKSBI7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KMBNG</t>
+          <t>KMBNG7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUTET DKSBI - MKRNG</t>
+          <t>SUTET DKSBI7 - MKRNG7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>DKSBI7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUTET MTWAR - CWANG</t>
+          <t>SUTET MTWAR7 - CWANG7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4676,17 +4676,17 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SUTET MTWAR - TMBUN</t>
+          <t>SUTET MTWAR7 - TMBUN7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4736,17 +4736,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUTET TMBUN - BKASI</t>
+          <t>SUTET TMBUN7 - BKASI7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TMBUN</t>
+          <t>TMBUN7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4794,17 +4794,17 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SUTET BKASI - MTWAR</t>
+          <t>SUTET BKASI7 - MTWAR7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4852,17 +4852,17 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUTET MTWAR - PRIDK</t>
+          <t>SUTET MTWAR7 - PRIDK7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4910,17 +4910,17 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUTET PRIDK - MKRNG</t>
+          <t>SUTET PRIDK7 - MKRNG7</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MKRNG</t>
+          <t>MKRNG7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4968,17 +4968,17 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUTET CWANG - GNDUL</t>
+          <t>SUTET CWANG7 - GNDUL7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CWANG</t>
+          <t>CWANG7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GNDUL</t>
+          <t>GNDUL7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5028,17 +5028,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUTET SKTNI - CLMYA</t>
+          <t>SUTET SKTNI7 - CLMYA7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5086,17 +5086,17 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUTET SKTNI - CBATU</t>
+          <t>SUTET SKTNI7 - CBATU7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5144,17 +5144,17 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUTET DLTMS - CBATU</t>
+          <t>SUTET DLTMS7 - CBATU7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DLTMS</t>
+          <t>DLTMS7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CBATU</t>
+          <t>CBATU7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5202,17 +5202,17 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUTET CRATA - SKTNI</t>
+          <t>SUTET CRATA7 - SKTNI7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>SKTNI7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5260,17 +5260,17 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUTET SGLNG - BDSLN</t>
+          <t>SUTET SGLNG7 - BDSLN7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5318,17 +5318,17 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUTET BDSLN - UBRNG</t>
+          <t>SUTET BDSLN7 - UBRNG7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5378,17 +5378,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUTET MDCAN - UBRNG</t>
+          <t>SUTET MDCAN7 - UBRNG7</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UBRNG</t>
+          <t>UBRNG7</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUTET MDCAN - BDSLN</t>
+          <t>SUTET MDCAN7 - BDSLN7</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5496,17 +5496,17 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUTET CIBNG - IDMYU</t>
+          <t>SUTET CIBNG7 - IDMYU7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>CIBNG7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5554,17 +5554,17 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUTET IDMYU - MDCAN</t>
+          <t>SUTET IDMYU7 - MDCAN7</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IDMYU7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5614,17 +5614,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUTET TSMYA - BDSLN</t>
+          <t>SUTET TSMYA7 - BDSLN7</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BDSLN</t>
+          <t>BDSLN7</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5674,17 +5674,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUTET TSMYA - DEPOK</t>
+          <t>SUTET TSMYA7 - DEPOK7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DEPOK</t>
+          <t>DEPOK7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUTET KSGHN - TSMYA</t>
+          <t>SUTET KSGHN7 - TSMYA7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TSMYA</t>
+          <t>TSMYA7</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5794,17 +5794,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SUTET KSGHN - ADPLA</t>
+          <t>SUTET KSGHN7 - ADPLA7</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5854,17 +5854,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUTET ADPLA - CLCAP</t>
+          <t>SUTET ADPLA7 - CLCAP7</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5914,17 +5914,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUTET PMLNG - BTANG</t>
+          <t>SUTET PMLNG7 - BTANG7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SUTET PMLNG - NTJTI</t>
+          <t>SUTET PMLNG7 - NTJTI7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUTET NTJTI - UNGRN</t>
+          <t>SUTET NTJTI7 - UNGRN7</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6094,17 +6094,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUTET TJATI - UNGRN</t>
+          <t>SUTET TJATI7 - UNGRN7</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6152,17 +6152,17 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUTET KSGHN - MDCAN</t>
+          <t>SUTET KSGHN7 - MDCAN7</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MDCAN</t>
+          <t>MDCAN7</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6210,17 +6210,17 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUTET KSGHN - PMLNG</t>
+          <t>SUTET KSGHN7 - PMLNG7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KSGHN</t>
+          <t>KSGHN7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PMLNG</t>
+          <t>PMLNG7</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6270,17 +6270,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUTET UNGRN - BYOLI</t>
+          <t>SUTET UNGRN7 - BYOLI7</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SUTET BYOLI - PEDAN</t>
+          <t>SUTET BYOLI7 - PEDAN7</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BYOLI</t>
+          <t>BYOLI7</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6388,17 +6388,17 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUTET UNGRN - KRIAN</t>
+          <t>SUTET UNGRN7 - KRIAN7</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6446,17 +6446,17 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUTET UNGRN - NBANG</t>
+          <t>SUTET UNGRN7 - NBANG7</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>UNGRN</t>
+          <t>UNGRN7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SUTET PITON - GRATI</t>
+          <t>SUTET PITON7 - GRATI7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUTET GRATI - KRIAN</t>
+          <t>SUTET GRATI7 - KRIAN7</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6624,17 +6624,17 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUTET PITON - KDIRI</t>
+          <t>SUTET PITON7 - KDIRI7</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUTET KDIRI - PEDAN</t>
+          <t>SUTET KDIRI7 - PEDAN7</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KDIRI</t>
+          <t>KDIRI7</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PEDAN</t>
+          <t>PEDAN7</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SUTET KRIAN - GRSIK</t>
+          <t>SUTET KRIAN7 - GRSIK7</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6800,17 +6800,17 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SUTET KRIAN - NBANG</t>
+          <t>SUTET KRIAN7 - NBANG7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KRIAN</t>
+          <t>KRIAN7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NBANG</t>
+          <t>NBANG7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6916,17 +6916,17 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Outlet KIT LBE</t>
+          <t>Outlet KIT LBE7</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KIT_LBE</t>
+          <t>KIT_LBE7</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>LBE</t>
+          <t>LBE7</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6974,17 +6974,17 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Outlet KIT NSRLA</t>
+          <t>Outlet KIT NSRLA7</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KIT_NSRLA</t>
+          <t>KIT_NSRLA7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NSRLA</t>
+          <t>NSRLA7</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7032,17 +7032,17 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Outlet KIT SRLYA</t>
+          <t>Outlet KIT SRLYA7</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KIT_SRLYA</t>
+          <t>KIT_SRLYA7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SRLYA</t>
+          <t>SRLYA7</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7090,17 +7090,17 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Outlet KIT JAWA910</t>
+          <t>Outlet KIT JAWA9107</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KIT_JAWA910</t>
+          <t>KIT_JAWA9107</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JAWA910</t>
+          <t>JAWA9107</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7148,17 +7148,17 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Outlet KIT PRIDK</t>
+          <t>Outlet KIT PRIDK7</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KIT_PRIDK</t>
+          <t>KIT_PRIDK7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PRIDK</t>
+          <t>PRIDK7</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7206,17 +7206,17 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Outlet KIT MTWAR</t>
+          <t>Outlet KIT MTWAR7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KIT_MTWAR</t>
+          <t>KIT_MTWAR7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MTWAR</t>
+          <t>MTWAR7</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7264,17 +7264,17 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Outlet KIT CLMYA</t>
+          <t>Outlet KIT CLMYA7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KIT_CLMYA</t>
+          <t>KIT_CLMYA7</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CLMYA</t>
+          <t>CLMYA7</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7322,17 +7322,17 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Outlet KIT CRATA</t>
+          <t>Outlet KIT CRATA7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KIT_CRATA</t>
+          <t>KIT_CRATA7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CRATA</t>
+          <t>CRATA7</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7380,17 +7380,17 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Outlet KIT SGLNG</t>
+          <t>Outlet KIT SGLNG7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KIT_SGLNG</t>
+          <t>KIT_SGLNG7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SGLNG</t>
+          <t>SGLNG7</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7438,17 +7438,17 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Outlet KIT ADPLA</t>
+          <t>Outlet KIT ADPLA7</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KIT_ADPLA</t>
+          <t>KIT_ADPLA7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ADPLA</t>
+          <t>ADPLA7</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7496,17 +7496,17 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Outlet KIT CLCAP</t>
+          <t>Outlet KIT CLCAP7</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KIT_CLCAP</t>
+          <t>KIT_CLCAP7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CLCAP</t>
+          <t>CLCAP7</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7554,17 +7554,17 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Outlet KIT BTANG</t>
+          <t>Outlet KIT BTANG7</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KIT_BTANG</t>
+          <t>KIT_BTANG7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BTANG</t>
+          <t>BTANG7</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7612,17 +7612,17 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Outlet KIT NTJTI</t>
+          <t>Outlet KIT NTJTI7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KIT_NTJTI</t>
+          <t>KIT_NTJTI7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NTJTI</t>
+          <t>NTJTI7</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7670,17 +7670,17 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Outlet KIT TJATI</t>
+          <t>Outlet KIT TJATI7</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KIT_TJATI</t>
+          <t>KIT_TJATI7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TJATI</t>
+          <t>TJATI7</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7728,17 +7728,17 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Outlet KIT GRSIK</t>
+          <t>Outlet KIT GRSIK7</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KIT_GRSIK</t>
+          <t>KIT_GRSIK7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GRSIK</t>
+          <t>GRSIK7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7786,17 +7786,17 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Outlet KIT GRATI</t>
+          <t>Outlet KIT GRATI7</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KIT_GRATI</t>
+          <t>KIT_GRATI7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GRATI</t>
+          <t>GRATI7</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7844,17 +7844,17 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Outlet KIT PITON</t>
+          <t>Outlet KIT PITON7</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KIT_PITON</t>
+          <t>KIT_PITON7</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PITON</t>
+          <t>PITON7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
